--- a/Exam/gymtrackerpro/lib/repository/__tests__/bbt/exercise-repository/setActive-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/repository/__tests__/bbt/exercise-repository/setActive-bbt-form.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="73">
   <si>
     <t>Statement: ExerciseRepository.setActive(id, isActive) – archives/restores an exercise.</t>
   </si>
@@ -136,19 +136,37 @@
     <t>ID length</t>
   </si>
   <si>
+    <t>id = "" (empty)</t>
+  </si>
+  <si>
+    <t>id = "a" (inexistent)</t>
+  </si>
+  <si>
+    <t>id = "a" (existing)</t>
+  </si>
+  <si>
+    <t>BVA</t>
+  </si>
+  <si>
+    <t>BVA-1 Empty</t>
+  </si>
+  <si>
     <t>id = ""</t>
   </si>
   <si>
-    <t>id = "a"</t>
-  </si>
-  <si>
-    <t>BVA</t>
-  </si>
-  <si>
-    <t>BVA-1 Empty</t>
-  </si>
-  <si>
-    <t>BVA-2 OneChar</t>
+    <t>BVA-2 InexChar</t>
+  </si>
+  <si>
+    <t>id = "a" (inex)</t>
+  </si>
+  <si>
+    <t>BVA-3 ExistChar</t>
+  </si>
+  <si>
+    <t>id = "a" (exist)</t>
+  </si>
+  <si>
+    <t>Updates successfully</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -173,6 +191,9 @@
   </si>
   <si>
     <t>BVA-2</t>
+  </si>
+  <si>
+    <t>BVA-3</t>
   </si>
   <si>
     <t>Testing</t>
@@ -902,7 +923,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -943,6 +964,17 @@
         <v>40</v>
       </c>
     </row>
+    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -951,7 +983,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -966,7 +998,7 @@
         <v>21</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>23</v>
@@ -983,10 +1015,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>35</v>
@@ -1000,15 +1032,32 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1020,7 +1069,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1036,10 +1085,10 @@
         <v>21</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>23</v>
@@ -1062,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>29</v>
@@ -1082,10 +1131,10 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>29</v>
@@ -1119,10 +1168,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>35</v>
@@ -1139,15 +1188,35 @@
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>35</v>
       </c>
       <c r="F6" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1176,16 +1245,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1193,45 +1262,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B3" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1240,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/repository/__tests__/bbt/exercise-repository/setActive-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/repository/__tests__/bbt/exercise-repository/setActive-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="73">
-  <si>
-    <t>Statement: ExerciseRepository.setActive(id, isActive) – archives/restores an exercise.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="63">
+  <si>
+    <t>Statement: ExerciseRepository.setActive(id, isActive) – Sets the isActive flag on an existing exercise. Returns the updated Exercise on success. Throws NotFoundError("Exercise not found") if no exercise exists with the given ID.</t>
   </si>
   <si>
     <t/>
@@ -37,19 +37,19 @@
     <t>precondition</t>
   </si>
   <si>
-    <t>Database is accessible</t>
+    <t>Database is accessible. An exercise with the given ID may or may not exist.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: Promise&lt;Exercise&gt; | throws NotFoundError</t>
+    <t>Output: Promise&lt;Exercise&gt;</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>isActive flag updated.</t>
+    <t>On success: Exercise returned with result.isActive matching the input value and result equal to expected. On failure: NotFoundError("Exercise not found") thrown.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -67,19 +67,13 @@
     <t>Exercise existence</t>
   </si>
   <si>
-    <t>Found</t>
-  </si>
-  <si>
-    <t>Not found (NotFoundError)</t>
-  </si>
-  <si>
-    <t>Active status</t>
-  </si>
-  <si>
-    <t>isActive = false</t>
-  </si>
-  <si>
-    <t>isActive = true</t>
+    <t>Existing ID, isActive: false → Exercise returned with result.isActive: false, result equal to expected</t>
+  </si>
+  <si>
+    <t>Existing ID, isActive: true → Exercise returned with result.isActive: true, result equal to expected</t>
+  </si>
+  <si>
+    <t>Non-existent ID → NotFoundError("Exercise not found")</t>
   </si>
   <si>
     <t>No TC</t>
@@ -97,34 +91,34 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>EC-1, EC-3</t>
-  </si>
-  <si>
-    <t>id exists, isActive=false</t>
-  </si>
-  <si>
-    <t>Returns isActive=false</t>
+    <t>EC-1</t>
+  </si>
+  <si>
+    <t>id: EXERCISE_ID, isActive: false (exercise exists, currently active)</t>
+  </si>
+  <si>
+    <t>Exercise returned with result.isActive: false, result equal to { ...MOCK_EXERCISE, isActive: false }</t>
   </si>
   <si>
     <t>Passed</t>
   </si>
   <si>
-    <t>EC-1, EC-4</t>
-  </si>
-  <si>
-    <t>id exists, isActive=true</t>
-  </si>
-  <si>
-    <t>Returns isActive=true</t>
-  </si>
-  <si>
     <t>EC-2</t>
   </si>
   <si>
-    <t>Non-existent ID</t>
-  </si>
-  <si>
-    <t>Throws NotFoundError</t>
+    <t>id: EXERCISE_ID, isActive: true (exercise exists, currently inactive)</t>
+  </si>
+  <si>
+    <t>Exercise returned with result.isActive: true, result equal to { ...MOCK_EXERCISE, isActive: true }</t>
+  </si>
+  <si>
+    <t>EC-3</t>
+  </si>
+  <si>
+    <t>id: "non-existent-id", isActive: true (no exercise with that ID)</t>
+  </si>
+  <si>
+    <t>throws NotFoundError("Exercise not found")</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -136,37 +130,31 @@
     <t>ID length</t>
   </si>
   <si>
-    <t>id = "" (empty)</t>
-  </si>
-  <si>
-    <t>id = "a" (inexistent)</t>
-  </si>
-  <si>
-    <t>id = "a" (existing)</t>
+    <t>0 chars (empty, not found), 1 char (not found), 1 char (found)</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>BVA-1 Empty</t>
-  </si>
-  <si>
-    <t>id = ""</t>
-  </si>
-  <si>
-    <t>BVA-2 InexChar</t>
-  </si>
-  <si>
-    <t>id = "a" (inex)</t>
-  </si>
-  <si>
-    <t>BVA-3 ExistChar</t>
-  </si>
-  <si>
-    <t>id = "a" (exist)</t>
-  </si>
-  <si>
-    <t>Updates successfully</t>
+    <t>BVA-1 (n=0)</t>
+  </si>
+  <si>
+    <t>id: "" (no exercise with that ID), isActive: true</t>
+  </si>
+  <si>
+    <t>throws NotFoundError</t>
+  </si>
+  <si>
+    <t>BVA-1 (n=1)</t>
+  </si>
+  <si>
+    <t>id: "a" (no exercise with that ID), isActive: true</t>
+  </si>
+  <si>
+    <t>id: "a" (exercise exists with id: "a", currently active), isActive: false</t>
+  </si>
+  <si>
+    <t>Exercise returned with result.id: "a", result.isActive: false</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -175,27 +163,9 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>Exist, set inactive</t>
-  </si>
-  <si>
-    <t>isActive=false</t>
-  </si>
-  <si>
-    <t>Exist, set active</t>
-  </si>
-  <si>
-    <t>isActive=true</t>
-  </si>
-  <si>
     <t>BVA-1</t>
   </si>
   <si>
-    <t>BVA-2</t>
-  </si>
-  <si>
-    <t>BVA-3</t>
-  </si>
-  <si>
     <t>Testing</t>
   </si>
   <si>
@@ -226,7 +196,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>EXM-04</t>
+    <t>REPO-17</t>
   </si>
   <si>
     <t>n/a</t>
@@ -751,7 +721,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -792,13 +762,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -806,27 +776,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -849,19 +805,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -869,16 +825,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -886,16 +842,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="E3" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -903,16 +859,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="E4" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -923,7 +879,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -933,13 +889,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -947,32 +903,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -995,19 +929,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1015,16 +949,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1032,16 +966,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1049,16 +983,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1082,22 +1016,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1105,19 +1039,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="F2" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1125,19 +1059,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="F3" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1145,19 +1079,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="F4" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1168,16 +1102,16 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1188,16 +1122,16 @@
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1208,16 +1142,16 @@
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1245,16 +1179,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1262,39 +1196,39 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B3" s="1">
         <v>6</v>
@@ -1309,19 +1243,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
